--- a/用卷/xlsx/常规科目/2018.xlsx
+++ b/用卷/xlsx/常规科目/2018.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\常规科目\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC748831-3424-4A1D-942A-7166EB19672C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A41A2BC-D326-4A6C-BA83-D267F88A5427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -609,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -673,6 +673,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1486,7 +1495,7 @@
       <c r="A45" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="22">
         <v>10</v>
       </c>
       <c r="C45" s="10" t="s">
@@ -1497,45 +1506,35 @@
       <c r="A46" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="2">
-        <v>10</v>
-      </c>
+      <c r="B46" s="23"/>
       <c r="C46" s="11"/>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="2">
-        <v>10</v>
-      </c>
+      <c r="B47" s="23"/>
       <c r="C47" s="11"/>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="2">
-        <v>10</v>
-      </c>
+      <c r="B48" s="23"/>
       <c r="C48" s="11"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="2">
-        <v>10</v>
-      </c>
+      <c r="B49" s="23"/>
       <c r="C49" s="11"/>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B50" s="2">
-        <v>10</v>
-      </c>
+      <c r="B50" s="24"/>
       <c r="C50" s="12"/>
     </row>
     <row r="51" spans="1:3">
@@ -1550,7 +1549,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="C45:C50"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A1:D1"/>
@@ -1561,6 +1560,7 @@
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B45:B50"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/用卷/xlsx/常规科目/2018.xlsx
+++ b/用卷/xlsx/常规科目/2018.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\常规科目\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A41A2BC-D326-4A6C-BA83-D267F88A5427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,15 +14,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="79" count="79">
   <si>
     <t>年份</t>
   </si>
@@ -46,7 +37,6 @@
   </si>
   <si>
     <t>全国1卷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>北京</t>
@@ -77,7 +67,6 @@
   </si>
   <si>
     <t>全国2卷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>辽宁</t>
@@ -90,7 +79,6 @@
   </si>
   <si>
     <t>上海春考</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>上海卷</t>
@@ -106,7 +94,6 @@
   </si>
   <si>
     <t>江苏卷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>浙江首考</t>
@@ -146,7 +133,6 @@
   </si>
   <si>
     <t>全国3卷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>海南</t>
@@ -183,7 +169,6 @@
   </si>
   <si>
     <t>分科卷数统计(英语只记录笔试)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>科目</t>
@@ -226,11 +211,9 @@
   </si>
   <si>
     <t>浙江11,4月卷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2018年普通高等学校招生全国统一考试用卷情况统计(语数英物化生政史地技)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>英语听力不计入总成绩,笔试分数乘1.25四舍五入等于总成绩</t>
@@ -241,11 +224,9 @@
   <si>
     <t>1.英语一共2次机会,取较高分数计入总成绩
 2.首考英语也作为合格性考试的一部分</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>英语听力一共2次机会,取较高成绩和笔试组成总成绩</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>英语听说考试笔试分数乘1.125四舍五入+听说考试分数/4四舍五入等于总成绩</t>
@@ -253,219 +234,171 @@
   <si>
     <t>1.英语一共2次机会,每次分为听说测试,听力和笔试,取2次中总成绩较高一次计入总成绩
 2.春考也作为合格性考试的一部分</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>英语听力不计入总成绩,笔试按阅读和七选五每题2'→3',完形1.5'→2'折算为总成绩</t>
   </si>
   <si>
     <t>听力两次机会,较高分数计入总成绩,均使用PETS-2试题</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>全国123卷文理</t>
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>,北京卷文理,天津卷文理,上海春秋考卷,江苏卷,浙江卷</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>全国123卷</t>
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>,北京卷,天津卷,上海春秋考卷,江苏卷,浙江卷</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>全国123卷</t>
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>,北京卷,天津一考,6月卷,上海春秋考卷,江苏卷,</t>
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>浙江11月</t>
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>,</t>
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>高考卷</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>全国123卷</t>
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>,北京卷,天津卷,上海等级考卷,江苏卷,浙江11,4月卷,</t>
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="11"/>
         <color rgb="FFC00000"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>海南卷</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>特别说明:对于上海市2018届高考的学生,可以在高二参加生物地理等级考,对于浙江省,可以在高二参加英语和选考科目考试,为了保证不同年份试卷不重复,只计入高三参加的考试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>语文、数学、英语为全国2卷,其他科目为海南卷</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="0" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
+      <name val="等线"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
       <b/>
+      <charset val="134"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
+      <name val="等线"/>
       <b/>
+      <charset val="134"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -488,6 +421,21 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -521,26 +469,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalDown="1">
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalDown="1">
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -555,9 +490,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -607,48 +540,49 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -656,47 +590,42 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16" count="0"/>
 </styleSheet>
 </file>
 
@@ -953,598 +882,593 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D51"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="14.25" defaultColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="79.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="89.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" bestFit="1" width="5.5" style="0"/>
+    <col min="2" max="2" customWidth="1" bestFit="1" width="11.0" style="0"/>
+    <col min="3" max="3" customWidth="1" bestFit="1" width="79.5" style="0"/>
+    <col min="4" max="4" customWidth="1" bestFit="1" width="89.375" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="8:8">
+      <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="8:8">
+      <c r="A2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="8:8">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="8:8">
+      <c r="A4" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="8:8">
+      <c r="A5" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="6" spans="8:8">
+      <c r="A6" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="8:8">
+      <c r="A7" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="8:8">
+      <c r="A8" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="8:8">
+      <c r="A9" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B10" s="4" t="s">
+    <row r="10" spans="8:8">
+      <c r="A10" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B11" s="4" t="s">
+    <row r="11" spans="8:8">
+      <c r="A11" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B12" s="4" t="s">
+    <row r="12" spans="8:8">
+      <c r="A12" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="8:8">
+      <c r="A13" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B14" s="4" t="s">
+    <row r="14" spans="8:8">
+      <c r="A14" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="8" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="7"/>
-      <c r="B15" s="5" t="s">
+    <row r="15" spans="8:8">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="8:8">
+      <c r="A16" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="C16" s="6"/>
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="A17" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="6"/>
-      <c r="B18" s="4" t="s">
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="A18" s="11"/>
+      <c r="B18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B19" s="4" t="s">
+    <row r="19" spans="8:8">
+      <c r="A19" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="C19" s="6"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="A20" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B21" s="4" t="s">
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="8:8">
+      <c r="A21" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="8:8">
+      <c r="A22" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="8:8">
+      <c r="A23" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B24" s="4" t="s">
+    <row r="24" spans="8:8">
+      <c r="A24" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B25" s="4" t="s">
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="8:8">
+      <c r="A25" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B26" s="4" t="s">
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="8:8">
+      <c r="A26" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B27" s="4" t="s">
+    <row r="27" spans="8:8">
+      <c r="A27" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B28" s="4" t="s">
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="8:8" ht="14.85">
+      <c r="A28" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="8:8">
+      <c r="A29" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="8:8">
+      <c r="A30" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="8:8">
+      <c r="A31" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="8:8">
+      <c r="A32" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="8:8">
+      <c r="A33" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="8:8">
+      <c r="A34" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="4" t="s">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="8:8">
+      <c r="A35" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="4" t="s">
+      <c r="D35" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="8:8">
+      <c r="A36" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="8:8">
+      <c r="A37" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="8:8">
+      <c r="A38" s="5">
+        <v>2018.0</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="8:8">
       <c r="A40" s="13" t="s">
         <v>49</v>
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="15"/>
     </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="8:8">
+      <c r="A41" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="8:8">
+      <c r="A42" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="2">
-        <v>9</v>
-      </c>
-      <c r="C42" s="1" t="s">
+      <c r="B42" s="17">
+        <v>9.0</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="8:8">
+      <c r="A43" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="2">
-        <v>14</v>
-      </c>
-      <c r="C43" s="1" t="s">
+      <c r="B43" s="17">
+        <v>14.0</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="8:8">
+      <c r="A44" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="2">
-        <v>11</v>
-      </c>
-      <c r="C44" s="1" t="s">
+      <c r="B44" s="17">
+        <v>11.0</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="8:8">
+      <c r="A45" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="22">
-        <v>10</v>
-      </c>
-      <c r="C45" s="10" t="s">
+      <c r="B45" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="C45" s="19" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="8:8">
+      <c r="A46" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="23"/>
-      <c r="C46" s="11"/>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
+      <c r="B46" s="20"/>
+      <c r="C46" s="21"/>
+    </row>
+    <row r="47" spans="8:8">
+      <c r="A47" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="23"/>
-      <c r="C47" s="11"/>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
+      <c r="B47" s="20"/>
+      <c r="C47" s="21"/>
+    </row>
+    <row r="48" spans="8:8">
+      <c r="A48" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="23"/>
-      <c r="C48" s="11"/>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
+      <c r="B48" s="20"/>
+      <c r="C48" s="21"/>
+    </row>
+    <row r="49" spans="8:8">
+      <c r="A49" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="23"/>
-      <c r="C49" s="11"/>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
+      <c r="B49" s="20"/>
+      <c r="C49" s="21"/>
+    </row>
+    <row r="50" spans="8:8">
+      <c r="A50" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B50" s="24"/>
-      <c r="C50" s="12"/>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
+      <c r="B50" s="22"/>
+      <c r="C50" s="23"/>
+    </row>
+    <row r="51" spans="8:8">
+      <c r="A51" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B51" s="2">
-        <v>2</v>
-      </c>
-      <c r="C51" s="3" t="s">
+      <c r="B51" s="17">
+        <v>2.0</v>
+      </c>
+      <c r="C51" s="24" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1552,6 +1476,7 @@
   <mergeCells count="11">
     <mergeCell ref="C45:C50"/>
     <mergeCell ref="A40:C40"/>
+    <mergeCell ref="B45:B50"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>
@@ -1560,9 +1485,7 @@
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B45:B50"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>